--- a/thvv/eval/效果验收标准.xlsx
+++ b/thvv/eval/效果验收标准.xlsx
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -529,6 +529,7 @@
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -542,7 +543,8 @@
       <c r="D1" s="6" t="n"/>
       <c r="E1" s="6" t="n"/>
       <c r="F1" s="6" t="n"/>
-      <c r="G1" s="7" t="n"/>
+      <c r="G1" s="6" t="n"/>
+      <c r="H1" s="7" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -577,6 +579,11 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
+          <t>glm-5.3</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>浮动范围</t>
         </is>
       </c>
@@ -604,7 +611,10 @@
       <c r="F3" s="4" t="n">
         <v>96</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="n">
+        <v>93.12</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>±2-4%</t>
         </is>
@@ -633,7 +643,10 @@
       <c r="F4" s="4" t="n">
         <v>34.33</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="n">
+        <v>40.18</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>±2-4%</t>
         </is>
@@ -662,7 +675,10 @@
       <c r="F5" s="4" t="n">
         <v>85.95999999999999</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="4" t="n">
+        <v>88.08</v>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>±2-4%</t>
         </is>
@@ -691,7 +707,10 @@
       <c r="F6" s="4" t="n">
         <v>33.7</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="4" t="n">
+        <v>39.37</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>±2-4%</t>
         </is>
@@ -720,7 +739,10 @@
       <c r="F7" s="4" t="n">
         <v>94.44</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="4" t="n">
+        <v>91.08</v>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>±2-4%</t>
         </is>
@@ -749,7 +771,10 @@
       <c r="F8" s="4" t="n">
         <v>67.56</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="4" t="n">
+        <v>67.58</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>±2-4%</t>
         </is>
@@ -778,7 +803,10 @@
       <c r="F9" s="4" t="n">
         <v>82.22</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="4" t="n">
+        <v>88.38</v>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>±2-4%</t>
         </is>
@@ -807,7 +835,10 @@
       <c r="F10" s="4" t="n">
         <v>77.14</v>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="4" t="n">
+        <v>94.20999999999999</v>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>±2-4%</t>
         </is>
@@ -836,7 +867,10 @@
       <c r="F11" s="4" t="n">
         <v>74.7</v>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>±2-4%</t>
         </is>
@@ -865,7 +899,10 @@
       <c r="F12" s="4" t="n">
         <v>77.27</v>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="4" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>±2-4%</t>
         </is>
@@ -898,7 +935,10 @@
       <c r="F13" s="4" t="n">
         <v>86.92</v>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="4" t="n">
+        <v>91.28</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>±2-4%</t>
         </is>
@@ -933,7 +973,10 @@
       <c r="F14" s="4" t="n">
         <v>85.42</v>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>±2-4%</t>
         </is>
@@ -950,12 +993,13 @@
       <c r="D16" s="6" t="n"/>
       <c r="E16" s="6" t="n"/>
       <c r="F16" s="6" t="n"/>
-      <c r="G16" s="7" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
